--- a/data/calendario.xlsx
+++ b/data/calendario.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RODRIGO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utmedu-my.sharepoint.com/personal/spmo_servicios_tecmilenio_mx/Documents/Efectividad Institucional/calendario-main/calendario-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAEF524-BBC9-4C57-A358-6D4B71EECDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{5CAEF524-BBC9-4C57-A358-6D4B71EECDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF4EA4AC-30F3-4238-A221-C25EE1B2888D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Catalogos" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datos!$A$1:$N$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datos!$A$1:$N$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="170">
   <si>
     <t>Calendario de Inteligencia y Efectividad Institucional</t>
   </si>
@@ -493,12 +493,6 @@
     <t>2026-12-21</t>
   </si>
   <si>
-    <t>2026-027</t>
-  </si>
-  <si>
-    <t>EM26 B1 P1</t>
-  </si>
-  <si>
     <t>Bloques</t>
   </si>
   <si>
@@ -511,78 +505,6 @@
     <t>Todos los niveles</t>
   </si>
   <si>
-    <t>2026-01-26</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>2026-028</t>
-  </si>
-  <si>
-    <t>EM26 B1 P2</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>2026-02-27</t>
-  </si>
-  <si>
-    <t>2026-029</t>
-  </si>
-  <si>
-    <t>EM26 B2 P1</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-030</t>
-  </si>
-  <si>
-    <t>EM26 B2 P2</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-031</t>
-  </si>
-  <si>
-    <t>AD26 B1 P1</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>2026-032</t>
-  </si>
-  <si>
-    <t>AD26 B1 P2</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>2026-033</t>
-  </si>
-  <si>
-    <t>AD26 B2 P1</t>
-  </si>
-  <si>
-    <t>2026-10-26</t>
-  </si>
-  <si>
-    <t>2026-034</t>
-  </si>
-  <si>
-    <t>AD26 B2 P2</t>
-  </si>
-  <si>
-    <t>2026-11-27</t>
-  </si>
-  <si>
     <t>2026-035</t>
   </si>
   <si>
@@ -620,12 +542,21 @@
   </si>
   <si>
     <t>MAPS Semestral</t>
+  </si>
+  <si>
+    <t>Preparatoria Tetramestral</t>
+  </si>
+  <si>
+    <t>Preparatoria y Profesional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -717,7 +648,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -738,7 +669,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1254,7 +1191,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="9" customWidth="1"/>
@@ -1262,14 +1199,14 @@
     <col min="3" max="3" width="19.85546875" style="9" customWidth="1"/>
     <col min="4" max="4" width="15" style="9" customWidth="1"/>
     <col min="5" max="5" width="28.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.42578125" style="9" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="22" style="9" customWidth="1"/>
+    <col min="6" max="6" width="37.42578125" style="9" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="9" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.28515625" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.42578125" style="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.42578125" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="29.42578125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="21.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.42578125" style="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="60" style="9" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="9"/>
   </cols>
@@ -1341,7 +1278,7 @@
         <v>48</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>49</v>
+        <v>169</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>50</v>
@@ -1352,7 +1289,9 @@
       <c r="K2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="10"/>
+      <c r="L2" s="13">
+        <v>46195</v>
+      </c>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
     </row>
@@ -1378,8 +1317,8 @@
       <c r="G3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>49</v>
+      <c r="H3" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>55</v>
@@ -1390,7 +1329,9 @@
       <c r="K3" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="14">
+        <v>46376</v>
+      </c>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
     </row>
@@ -1428,7 +1369,9 @@
       <c r="K4" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="10"/>
+      <c r="L4" s="13">
+        <v>46195</v>
+      </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
     </row>
@@ -1466,7 +1409,9 @@
       <c r="K5" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="L5" s="11"/>
+      <c r="L5" s="14">
+        <v>46376</v>
+      </c>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
@@ -1504,7 +1449,9 @@
       <c r="K6" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="10"/>
+      <c r="L6" s="13">
+        <v>46195</v>
+      </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
     </row>
@@ -1542,7 +1489,9 @@
       <c r="K7" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="L7" s="11"/>
+      <c r="L7" s="14">
+        <v>46255</v>
+      </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
     </row>
@@ -1580,7 +1529,9 @@
       <c r="K8" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L8" s="10"/>
+      <c r="L8" s="14">
+        <v>46376</v>
+      </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
     </row>
@@ -1618,7 +1569,9 @@
       <c r="K9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="L9" s="11"/>
+      <c r="L9" s="13">
+        <v>46195</v>
+      </c>
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
     </row>
@@ -1656,7 +1609,9 @@
       <c r="K10" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="L10" s="10"/>
+      <c r="L10" s="14">
+        <v>46255</v>
+      </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
     </row>
@@ -1694,7 +1649,9 @@
       <c r="K11" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="11"/>
+      <c r="L11" s="14">
+        <v>46376</v>
+      </c>
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
     </row>
@@ -1721,7 +1678,7 @@
         <v>48</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>72</v>
@@ -1732,7 +1689,9 @@
       <c r="K12" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="10"/>
+      <c r="L12" s="13">
+        <v>46134</v>
+      </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
     </row>
@@ -1758,8 +1717,8 @@
       <c r="G13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>87</v>
+      <c r="H13" s="10" t="s">
+        <v>168</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>76</v>
@@ -1770,7 +1729,9 @@
       <c r="K13" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="L13" s="11"/>
+      <c r="L13" s="14">
+        <v>46255</v>
+      </c>
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
     </row>
@@ -1797,7 +1758,7 @@
         <v>48</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>55</v>
@@ -1808,7 +1769,9 @@
       <c r="K14" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L14" s="10"/>
+      <c r="L14" s="13">
+        <v>46376</v>
+      </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
     </row>
@@ -1835,7 +1798,7 @@
         <v>48</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>72</v>
@@ -1846,7 +1809,9 @@
       <c r="K15" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="L15" s="11"/>
+      <c r="L15" s="13">
+        <v>46195</v>
+      </c>
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
     </row>
@@ -1873,7 +1838,7 @@
         <v>48</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>95</v>
@@ -1884,7 +1849,9 @@
       <c r="K16" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="L16" s="10"/>
+      <c r="L16" s="14">
+        <v>46259</v>
+      </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
     </row>
@@ -1911,7 +1878,7 @@
         <v>48</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>99</v>
@@ -1922,7 +1889,9 @@
       <c r="K17" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="L17" s="11"/>
+      <c r="L17" s="14">
+        <v>46376</v>
+      </c>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
@@ -1949,7 +1918,7 @@
         <v>48</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>105</v>
@@ -1960,7 +1929,7 @@
       <c r="K18" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="L18" s="13" t="s">
         <v>108</v>
       </c>
       <c r="M18" s="10"/>
@@ -1989,7 +1958,7 @@
         <v>48</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>111</v>
@@ -2000,7 +1969,7 @@
       <c r="K19" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="14" t="s">
         <v>114</v>
       </c>
       <c r="M19" s="11"/>
@@ -2029,7 +1998,7 @@
         <v>48</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>117</v>
@@ -2040,7 +2009,7 @@
       <c r="K20" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="L20" s="10" t="s">
+      <c r="L20" s="13" t="s">
         <v>120</v>
       </c>
       <c r="M20" s="10"/>
@@ -2069,7 +2038,7 @@
         <v>48</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>66</v>
@@ -2080,7 +2049,7 @@
       <c r="K21" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L21" s="14" t="s">
         <v>124</v>
       </c>
       <c r="M21" s="11"/>
@@ -2109,7 +2078,7 @@
         <v>48</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>128</v>
@@ -2120,7 +2089,7 @@
       <c r="K22" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L22" s="10" t="s">
+      <c r="L22" s="13" t="s">
         <v>131</v>
       </c>
       <c r="M22" s="10"/>
@@ -2149,7 +2118,7 @@
         <v>48</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>134</v>
@@ -2160,7 +2129,7 @@
       <c r="K23" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L23" s="14" t="s">
         <v>137</v>
       </c>
       <c r="M23" s="11"/>
@@ -2191,7 +2160,7 @@
         <v>48</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>141</v>
@@ -2202,7 +2171,7 @@
       <c r="K24" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="L24" s="10" t="s">
+      <c r="L24" s="13" t="s">
         <v>124</v>
       </c>
       <c r="M24" s="10"/>
@@ -2242,7 +2211,7 @@
       <c r="K25" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="14" t="s">
         <v>131</v>
       </c>
       <c r="M25" s="11"/>
@@ -2282,7 +2251,7 @@
       <c r="K26" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="L26" s="10" t="s">
+      <c r="L26" s="13" t="s">
         <v>137</v>
       </c>
       <c r="M26" s="10"/>
@@ -2322,7 +2291,7 @@
       <c r="K27" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="14">
         <v>46397</v>
       </c>
       <c r="M27" s="11"/>
@@ -2330,369 +2299,90 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B28" s="10">
         <v>2026</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>152</v>
+        <v>44</v>
       </c>
       <c r="D28" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" s="10"/>
+      <c r="H28" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I28" s="12">
+        <v>46146</v>
+      </c>
       <c r="J28" s="10" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="L28" s="10"/>
+        <v>156</v>
+      </c>
+      <c r="L28" s="13">
+        <v>46178</v>
+      </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B29" s="11">
         <v>2026</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="D29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>48</v>
-      </c>
       <c r="H29" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I29" s="11"/>
+        <v>153</v>
+      </c>
+      <c r="I29" s="12">
+        <v>46349</v>
+      </c>
       <c r="J29" s="11" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="L29" s="11"/>
+        <v>123</v>
+      </c>
+      <c r="L29" s="13">
+        <v>46374</v>
+      </c>
       <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B30" s="10">
-        <v>2026</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B31" s="11">
-        <v>2026</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" s="10">
-        <v>2026</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B33" s="11">
-        <v>2026</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="B34" s="10">
-        <v>2026</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B35" s="11">
-        <v>2026</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B36" s="10">
-        <v>2026</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B37" s="11">
-        <v>2026</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11" t="s">
-        <v>184</v>
+      <c r="N29" s="11" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N37" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:N29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
@@ -2700,19 +2390,19 @@
           <x14:formula1>
             <xm:f>Catalogos!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D497</xm:sqref>
+          <xm:sqref>D2:D489</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000002000000}">
           <x14:formula1>
             <xm:f>Catalogos!$C$2:$C$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F497</xm:sqref>
+          <xm:sqref>F2:F489</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
           <x14:formula1>
             <xm:f>Catalogos!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G497</xm:sqref>
+          <xm:sqref>G2:G489</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
@@ -2785,7 +2475,7 @@
         <v>60</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>49</v>
@@ -2796,13 +2486,13 @@
         <v>104</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
@@ -2810,10 +2500,10 @@
         <v>127</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>71</v>
@@ -2821,24 +2511,24 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="D7" s="7" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
@@ -2848,15 +2538,21 @@
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="E9" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="E10" s="7" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{030e951d-6efd-42f5-8427-bab632cf8010}" enabled="0" method="" siteId="{030e951d-6efd-42f5-8427-bab632cf8010}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/data/calendario.xlsx
+++ b/data/calendario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utmedu-my.sharepoint.com/personal/spmo_servicios_tecmilenio_mx/Documents/Efectividad Institucional/calendario-main/calendario-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{5CAEF524-BBC9-4C57-A358-6D4B71EECDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF4EA4AC-30F3-4238-A221-C25EE1B2888D}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{5CAEF524-BBC9-4C57-A358-6D4B71EECDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60BBEDA6-E730-49DC-B8E2-F28BF948C682}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="172">
   <si>
     <t>Calendario de Inteligencia y Efectividad Institucional</t>
   </si>
@@ -454,9 +454,6 @@
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>Bloque junio–julio 26.</t>
-  </si>
-  <si>
     <t>2026-023</t>
   </si>
   <si>
@@ -514,9 +511,6 @@
     <t>2026-036</t>
   </si>
   <si>
-    <t>Revisar: el archivo decía 'lunes 30 de diciembre al viernes 11 de diciembre' (el fin cae antes del inicio).</t>
-  </si>
-  <si>
     <t>Egresados</t>
   </si>
   <si>
@@ -548,6 +542,18 @@
   </si>
   <si>
     <t>Preparatoria y Profesional</t>
+  </si>
+  <si>
+    <t>Educación Remota</t>
+  </si>
+  <si>
+    <t>Regionales Académicos</t>
+  </si>
+  <si>
+    <t>Gestión Docente Regional</t>
+  </si>
+  <si>
+    <t>Gestión Académica Regional</t>
   </si>
 </sst>
 </file>
@@ -555,7 +561,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -672,10 +678,10 @@
     <xf numFmtId="14" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1199,14 +1205,14 @@
     <col min="3" max="3" width="19.85546875" style="9" customWidth="1"/>
     <col min="4" max="4" width="15" style="9" customWidth="1"/>
     <col min="5" max="5" width="28.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.42578125" style="9" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" style="9" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="37.42578125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="9" customWidth="1"/>
     <col min="8" max="8" width="25.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" style="9" customWidth="1"/>
     <col min="12" max="12" width="29.42578125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="23.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="60" style="9" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="9"/>
   </cols>
@@ -1278,7 +1284,7 @@
         <v>48</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>50</v>
@@ -1292,7 +1298,9 @@
       <c r="L2" s="13">
         <v>46195</v>
       </c>
-      <c r="M2" s="10"/>
+      <c r="M2" s="10" t="s">
+        <v>171</v>
+      </c>
       <c r="N2" s="10"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1318,7 +1326,7 @@
         <v>48</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>55</v>
@@ -1332,7 +1340,9 @@
       <c r="L3" s="14">
         <v>46376</v>
       </c>
-      <c r="M3" s="11"/>
+      <c r="M3" s="10" t="s">
+        <v>171</v>
+      </c>
       <c r="N3" s="11"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1372,7 +1382,9 @@
       <c r="L4" s="13">
         <v>46195</v>
       </c>
-      <c r="M4" s="10"/>
+      <c r="M4" s="10" t="s">
+        <v>171</v>
+      </c>
       <c r="N4" s="10"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1412,7 +1424,9 @@
       <c r="L5" s="14">
         <v>46376</v>
       </c>
-      <c r="M5" s="11"/>
+      <c r="M5" s="10" t="s">
+        <v>169</v>
+      </c>
       <c r="N5" s="11"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1452,7 +1466,9 @@
       <c r="L6" s="13">
         <v>46195</v>
       </c>
-      <c r="M6" s="10"/>
+      <c r="M6" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N6" s="10"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1492,7 +1508,9 @@
       <c r="L7" s="14">
         <v>46255</v>
       </c>
-      <c r="M7" s="11"/>
+      <c r="M7" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N7" s="11"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1527,12 +1545,14 @@
         <v>66</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="L8" s="14">
         <v>46376</v>
       </c>
-      <c r="M8" s="10"/>
+      <c r="M8" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N8" s="10"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1572,7 +1592,9 @@
       <c r="L9" s="13">
         <v>46195</v>
       </c>
-      <c r="M9" s="11"/>
+      <c r="M9" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N9" s="11"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1612,7 +1634,9 @@
       <c r="L10" s="14">
         <v>46255</v>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N10" s="10"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -1652,7 +1676,9 @@
       <c r="L11" s="14">
         <v>46376</v>
       </c>
-      <c r="M11" s="11"/>
+      <c r="M11" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N11" s="11"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1678,7 +1704,7 @@
         <v>48</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>72</v>
@@ -1692,7 +1718,9 @@
       <c r="L12" s="13">
         <v>46134</v>
       </c>
-      <c r="M12" s="10"/>
+      <c r="M12" s="10" t="s">
+        <v>171</v>
+      </c>
       <c r="N12" s="10"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1718,7 +1746,7 @@
         <v>48</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>76</v>
@@ -1732,7 +1760,9 @@
       <c r="L13" s="14">
         <v>46255</v>
       </c>
-      <c r="M13" s="11"/>
+      <c r="M13" s="10" t="s">
+        <v>171</v>
+      </c>
       <c r="N13" s="11"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1758,7 +1788,7 @@
         <v>48</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>55</v>
@@ -1772,7 +1802,9 @@
       <c r="L14" s="13">
         <v>46376</v>
       </c>
-      <c r="M14" s="10"/>
+      <c r="M14" s="10" t="s">
+        <v>171</v>
+      </c>
       <c r="N14" s="10"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1798,7 +1830,7 @@
         <v>48</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>72</v>
@@ -1812,7 +1844,9 @@
       <c r="L15" s="13">
         <v>46195</v>
       </c>
-      <c r="M15" s="11"/>
+      <c r="M15" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N15" s="11"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -1838,7 +1872,7 @@
         <v>48</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>95</v>
@@ -1852,7 +1886,9 @@
       <c r="L16" s="14">
         <v>46259</v>
       </c>
-      <c r="M16" s="10"/>
+      <c r="M16" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N16" s="10"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1878,7 +1914,7 @@
         <v>48</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>99</v>
@@ -1892,7 +1928,9 @@
       <c r="L17" s="14">
         <v>46376</v>
       </c>
-      <c r="M17" s="11"/>
+      <c r="M17" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N17" s="11"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -1918,7 +1956,7 @@
         <v>48</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>105</v>
@@ -1932,7 +1970,9 @@
       <c r="L18" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="M18" s="10"/>
+      <c r="M18" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N18" s="10"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -1958,7 +1998,7 @@
         <v>48</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>111</v>
@@ -1972,7 +2012,9 @@
       <c r="L19" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="M19" s="11"/>
+      <c r="M19" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N19" s="11"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -1998,7 +2040,7 @@
         <v>48</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>117</v>
@@ -2012,7 +2054,9 @@
       <c r="L20" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="M20" s="10"/>
+      <c r="M20" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -2038,7 +2082,7 @@
         <v>48</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>66</v>
@@ -2052,7 +2096,9 @@
       <c r="L21" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="M21" s="11"/>
+      <c r="M21" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N21" s="11"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -2078,7 +2124,7 @@
         <v>48</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>128</v>
@@ -2092,7 +2138,9 @@
       <c r="L22" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="M22" s="10"/>
+      <c r="M22" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N22" s="10"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -2118,7 +2166,7 @@
         <v>48</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>134</v>
@@ -2132,20 +2180,20 @@
       <c r="L23" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11" t="s">
-        <v>138</v>
-      </c>
+      <c r="M23" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="N23" s="11"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2026</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="B24" s="10">
-        <v>2026</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>127</v>
@@ -2160,26 +2208,28 @@
         <v>48</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>82</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L24" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="M24" s="10"/>
+      <c r="M24" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N24" s="10"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B25" s="11">
         <v>2026</v>
@@ -2200,26 +2250,28 @@
         <v>48</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>128</v>
       </c>
       <c r="J25" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="K25" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>146</v>
       </c>
       <c r="L25" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="M25" s="11"/>
+      <c r="M25" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B26" s="10">
         <v>2026</v>
@@ -2240,7 +2292,7 @@
         <v>48</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>134</v>
@@ -2254,18 +2306,20 @@
       <c r="L26" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="M26" s="10"/>
+      <c r="M26" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N26" s="10"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B27" s="11">
         <v>2026</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>127</v>
@@ -2280,26 +2334,28 @@
         <v>48</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J27" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="L27" s="14">
         <v>46397</v>
       </c>
-      <c r="M27" s="11"/>
+      <c r="M27" s="10" t="s">
+        <v>168</v>
+      </c>
       <c r="N27" s="11"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B28" s="10">
         <v>2026</v>
@@ -2311,35 +2367,37 @@
         <v>45</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I28" s="12">
         <v>46146</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L28" s="13">
         <v>46178</v>
       </c>
-      <c r="M28" s="10"/>
+      <c r="M28" s="10" t="s">
+        <v>170</v>
+      </c>
       <c r="N28" s="10"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B29" s="11">
         <v>2026</v>
@@ -2351,16 +2409,16 @@
         <v>45</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I29" s="12">
         <v>46349</v>
@@ -2374,10 +2432,10 @@
       <c r="L29" s="13">
         <v>46374</v>
       </c>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11" t="s">
-        <v>158</v>
-      </c>
+      <c r="M29" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N29" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -2475,7 +2533,7 @@
         <v>60</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>49</v>
@@ -2486,13 +2544,13 @@
         <v>104</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
@@ -2500,10 +2558,10 @@
         <v>127</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>71</v>
@@ -2511,39 +2569,39 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="D7" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="E8" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="E9" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="E10" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
